--- a/docs/A2-1000.xlsx
+++ b/docs/A2-1000.xlsx
@@ -443,10 +443,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Attachment</v>
+        <v>Comment</v>
       </c>
       <c r="B4" t="str">
-        <v>Ek, dosya eki</v>
+        <v>Yorum, görüş</v>
       </c>
       <c r="C4" t="str">
         <v>Noun</v>
@@ -471,13 +471,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Broadband</v>
+        <v>Communicate</v>
       </c>
       <c r="B6" t="str">
-        <v>Geniş bant internet</v>
+        <v>İletişim kurmak, haberleşmek</v>
       </c>
       <c r="C6" t="str">
-        <v>Noun</v>
+        <v>Verb</v>
       </c>
       <c r="D6" t="str">
         <v>Communication and Technology</v>
@@ -583,13 +583,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Display</v>
+        <v>Image</v>
       </c>
       <c r="B14" t="str">
-        <v>Ekran, sergilemek</v>
+        <v>Görüntü, resim</v>
       </c>
       <c r="C14" t="str">
-        <v>Noun / Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D14" t="str">
         <v>Communication and Technology</v>
@@ -625,13 +625,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Hardware</v>
+        <v>Electronic</v>
       </c>
       <c r="B17" t="str">
-        <v>Donanım</v>
+        <v>Elektronik</v>
       </c>
       <c r="C17" t="str">
-        <v>Noun</v>
+        <v>Adjective</v>
       </c>
       <c r="D17" t="str">
         <v>Communication and Technology</v>
@@ -639,13 +639,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Install</v>
+        <v>Technology</v>
       </c>
       <c r="B18" t="str">
-        <v>Kurmak, yüklemek</v>
+        <v>Teknoloji</v>
       </c>
       <c r="C18" t="str">
-        <v>Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D18" t="str">
         <v>Communication and Technology</v>
@@ -709,13 +709,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Monitor</v>
+        <v>System</v>
       </c>
       <c r="B23" t="str">
-        <v>Monitör, izlemek</v>
+        <v>Sistem</v>
       </c>
       <c r="C23" t="str">
-        <v>Noun / Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D23" t="str">
         <v>Communication and Technology</v>
@@ -947,13 +947,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Upgrade</v>
+        <v>Code</v>
       </c>
       <c r="B40" t="str">
-        <v>Yükseltmek, seviye atlatmak</v>
+        <v>Kod, şifre</v>
       </c>
       <c r="C40" t="str">
-        <v>Verb / Noun</v>
+        <v>Noun</v>
       </c>
       <c r="D40" t="str">
         <v>Communication and Technology</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Cabin</v>
+        <v>Bridge</v>
       </c>
       <c r="B56" t="str">
-        <v>Kabin, kamara</v>
+        <v>Köprü</v>
       </c>
       <c r="C56" t="str">
         <v>Noun</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Cruise</v>
+        <v>Van</v>
       </c>
       <c r="B61" t="str">
-        <v>Gemi seyahati</v>
+        <v>Kamyonet, minibüs</v>
       </c>
       <c r="C61" t="str">
         <v>Noun</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Fare</v>
+        <v>Transport</v>
       </c>
       <c r="B70" t="str">
-        <v>Bilet ücreti, yol parası</v>
+        <v>Ulaşım, taşımacılık</v>
       </c>
       <c r="C70" t="str">
         <v>Noun</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Highway</v>
+        <v>Distance</v>
       </c>
       <c r="B74" t="str">
-        <v>Otoyol, karayolu</v>
+        <v>Mesafe, uzaklık</v>
       </c>
       <c r="C74" t="str">
         <v>Noun</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Terminal</v>
+        <v>Traveller</v>
       </c>
       <c r="B91" t="str">
-        <v>Terminal, son durak</v>
+        <v>Gezgin, yolcu</v>
       </c>
       <c r="C91" t="str">
         <v>Noun</v>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Lawn</v>
+        <v>Stair</v>
       </c>
       <c r="B126" t="str">
-        <v>Çim, çimenlik</v>
+        <v>Merdiven basamağı</v>
       </c>
       <c r="C126" t="str">
         <v>Noun</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Plug</v>
+        <v>Bin</v>
       </c>
       <c r="B131" t="str">
-        <v>Priz fişi, tıkaç</v>
+        <v>Çöp kutusu</v>
       </c>
       <c r="C131" t="str">
         <v>Noun</v>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Stir</v>
+        <v>Chip</v>
       </c>
       <c r="B201" t="str">
-        <v>Karıştırmak (kaşıkla)</v>
+        <v>Patates kızartması, cips</v>
       </c>
       <c r="C201" t="str">
-        <v>Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D201" t="str">
         <v>Food and Drink</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Accountant</v>
+        <v>Researcher</v>
       </c>
       <c r="B209" t="str">
-        <v>Muhasebeci</v>
+        <v>Araştırmacı</v>
       </c>
       <c r="C209" t="str">
         <v>Noun</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Applicant</v>
+        <v>Author</v>
       </c>
       <c r="B210" t="str">
-        <v>İş başvurusunda bulunan kişi</v>
+        <v>Yazar</v>
       </c>
       <c r="C210" t="str">
         <v>Noun</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Bonus</v>
+        <v>Businessman</v>
       </c>
       <c r="B213" t="str">
-        <v>İkramiye, prim</v>
+        <v>İş adamı</v>
       </c>
       <c r="C213" t="str">
         <v>Noun</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Contract</v>
+        <v>Deal</v>
       </c>
       <c r="B219" t="str">
-        <v>Sözleşme, kontrat</v>
+        <v>Anlaşma, uzlaşma</v>
       </c>
       <c r="C219" t="str">
-        <v>Noun</v>
+        <v>Noun / Verb</v>
       </c>
       <c r="D219" t="str">
         <v>Work and Jobs</v>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Income</v>
+        <v>Opportunity</v>
       </c>
       <c r="B234" t="str">
-        <v>Gelir, kazanç</v>
+        <v>Fırsat, imkân</v>
       </c>
       <c r="C234" t="str">
         <v>Noun</v>
@@ -3775,10 +3775,10 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Pension</v>
+        <v>Service</v>
       </c>
       <c r="B242" t="str">
-        <v>Emekli maaşı</v>
+        <v>Hizmet, servis</v>
       </c>
       <c r="C242" t="str">
         <v>Noun</v>
@@ -3831,10 +3831,10 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Promotion</v>
+        <v>Progress</v>
       </c>
       <c r="B246" t="str">
-        <v>Terfi, tanıtım</v>
+        <v>İlerleme, gelişim</v>
       </c>
       <c r="C246" t="str">
         <v>Noun</v>
@@ -3887,10 +3887,10 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Resign</v>
+        <v>Employ</v>
       </c>
       <c r="B250" t="str">
-        <v>İstifa etmek</v>
+        <v>İşe almak, çalıştırmak</v>
       </c>
       <c r="C250" t="str">
         <v>Verb</v>
@@ -3985,13 +3985,13 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Strike</v>
+        <v>Law</v>
       </c>
       <c r="B257" t="str">
-        <v>Grev, grev yapmak</v>
+        <v>Hukuk, yasa, kanun</v>
       </c>
       <c r="C257" t="str">
-        <v>Noun / Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D257" t="str">
         <v>Work and Jobs</v>
@@ -3999,10 +3999,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Surgeon</v>
+        <v>Professor</v>
       </c>
       <c r="B258" t="str">
-        <v>Cerrah</v>
+        <v>Profesör</v>
       </c>
       <c r="C258" t="str">
         <v>Noun</v>
@@ -4069,10 +4069,10 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Wage</v>
+        <v>Rate</v>
       </c>
       <c r="B263" t="str">
-        <v>Haftalık ücret, yevmiye</v>
+        <v>Oran, tarife, ücret seviyesi</v>
       </c>
       <c r="C263" t="str">
         <v>Noun</v>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Academy</v>
+        <v>Lecture</v>
       </c>
       <c r="B266" t="str">
-        <v>Akademi, enstitü</v>
+        <v>Ders, konferans</v>
       </c>
       <c r="C266" t="str">
         <v>Noun</v>
@@ -4195,10 +4195,10 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Certificate</v>
+        <v>Award</v>
       </c>
       <c r="B272" t="str">
-        <v>Sertifika, belge</v>
+        <v>Ödül, başarı belgesi</v>
       </c>
       <c r="C272" t="str">
         <v>Noun</v>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Intermediate</v>
+        <v>Teaching</v>
       </c>
       <c r="B286" t="str">
-        <v>Orta seviye</v>
+        <v>Öğretim, öğretmenlik</v>
       </c>
       <c r="C286" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D286" t="str">
         <v>Education and Learning</v>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Principal</v>
+        <v>Learning</v>
       </c>
       <c r="B295" t="str">
-        <v>Okul müdürü</v>
+        <v>Öğrenme, tahsil</v>
       </c>
       <c r="C295" t="str">
         <v>Noun</v>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pupil</v>
+        <v>Education</v>
       </c>
       <c r="B297" t="str">
-        <v>Öğrenci (ilköğretim)</v>
+        <v>Eğitim, tahsil</v>
       </c>
       <c r="C297" t="str">
         <v>Noun</v>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Scholarship</v>
+        <v>Chance</v>
       </c>
       <c r="B302" t="str">
-        <v>Burs</v>
+        <v>Şans, olanak, fırsat</v>
       </c>
       <c r="C302" t="str">
         <v>Noun</v>
@@ -4769,13 +4769,13 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Bleed</v>
+        <v>Accident</v>
       </c>
       <c r="B313" t="str">
-        <v>Kanamak</v>
+        <v>Kaza</v>
       </c>
       <c r="C313" t="str">
-        <v>Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D313" t="str">
         <v>Health and Body</v>
@@ -4895,10 +4895,10 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Clinic</v>
+        <v>Lab</v>
       </c>
       <c r="B322" t="str">
-        <v>Klinik, poliklinik</v>
+        <v>Laboratuvar</v>
       </c>
       <c r="C322" t="str">
         <v>Noun</v>
@@ -4923,13 +4923,13 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Cure</v>
+        <v>Danger</v>
       </c>
       <c r="B324" t="str">
-        <v>İyileştirmek, tedavi</v>
+        <v>Tehlike, risk</v>
       </c>
       <c r="C324" t="str">
-        <v>Verb / Noun</v>
+        <v>Noun</v>
       </c>
       <c r="D324" t="str">
         <v>Health and Body</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Healthcare</v>
+        <v>Condition</v>
       </c>
       <c r="B339" t="str">
-        <v>Sağlık hizmeti</v>
+        <v>Durum, sağlık durumu</v>
       </c>
       <c r="C339" t="str">
         <v>Noun</v>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Infection</v>
+        <v>Energy</v>
       </c>
       <c r="B340" t="str">
-        <v>Enfeksiyon, iltihap</v>
+        <v>Enerji, güç, zindelik</v>
       </c>
       <c r="C340" t="str">
         <v>Noun</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Prescription</v>
+        <v>Drug</v>
       </c>
       <c r="B349" t="str">
-        <v>Doktor reçetesi</v>
+        <v>İlaç, ecza</v>
       </c>
       <c r="C349" t="str">
         <v>Noun</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Pulse</v>
+        <v>Weight</v>
       </c>
       <c r="B350" t="str">
-        <v>Nabız</v>
+        <v>Kilo, ağırlık</v>
       </c>
       <c r="C350" t="str">
         <v>Noun</v>
@@ -5315,10 +5315,10 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Recovery</v>
+        <v>Habit</v>
       </c>
       <c r="B352" t="str">
-        <v>İyileşme dönemi</v>
+        <v>Alışkanlık</v>
       </c>
       <c r="C352" t="str">
         <v>Noun</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Surgery</v>
+        <v>Attack</v>
       </c>
       <c r="B359" t="str">
-        <v>Cerrahi müdahale, ameliyat</v>
+        <v>Kriz, atak, hücum</v>
       </c>
       <c r="C359" t="str">
         <v>Noun</v>
@@ -5539,13 +5539,13 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Ward</v>
+        <v>Care</v>
       </c>
       <c r="B368" t="str">
-        <v>Hastane koğuşu</v>
+        <v>Bakım, özen göstermek</v>
       </c>
       <c r="C368" t="str">
-        <v>Noun</v>
+        <v>Noun / Verb</v>
       </c>
       <c r="D368" t="str">
         <v>Health and Body</v>
@@ -5553,13 +5553,13 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Wound</v>
+        <v>Hole</v>
       </c>
       <c r="B369" t="str">
-        <v>Yara, yaralamak</v>
+        <v>Delik, çukur, yara boşluğu</v>
       </c>
       <c r="C369" t="str">
-        <v>Noun / Verb</v>
+        <v>Noun</v>
       </c>
       <c r="D369" t="str">
         <v>Health and Body</v>
@@ -5637,13 +5637,13 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Anxious</v>
+        <v>Stress</v>
       </c>
       <c r="B375" t="str">
-        <v>Endişeli, kaygılı</v>
+        <v>Stres, gerginlik</v>
       </c>
       <c r="C375" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D375" t="str">
         <v>Feelings and Emotions</v>
@@ -5651,13 +5651,13 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Ashamed</v>
+        <v>Trouble</v>
       </c>
       <c r="B376" t="str">
-        <v>Utanmış, mahcup</v>
+        <v>Dert, sıkıntı, bela</v>
       </c>
       <c r="C376" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D376" t="str">
         <v>Feelings and Emotions</v>
@@ -5749,13 +5749,13 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Depressed</v>
+        <v>Disaster</v>
       </c>
       <c r="B383" t="str">
-        <v>Bunalımlı, morali bozuk</v>
+        <v>Felaket, yıkım</v>
       </c>
       <c r="C383" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D383" t="str">
         <v>Feelings and Emotions</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Hopeful</v>
+        <v>Surprising</v>
       </c>
       <c r="B391" t="str">
-        <v>Umutlu, ümitvar</v>
+        <v>Şaşırtıcı</v>
       </c>
       <c r="C391" t="str">
         <v>Adjective</v>
@@ -5973,13 +5973,13 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Relieved</v>
+        <v>Peace</v>
       </c>
       <c r="B399" t="str">
-        <v>İçi rahatlamış</v>
+        <v>Huzur, barış</v>
       </c>
       <c r="C399" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D399" t="str">
         <v>Feelings and Emotions</v>
@@ -5987,13 +5987,13 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Satisfied</v>
+        <v>Sense</v>
       </c>
       <c r="B400" t="str">
-        <v>Tatmin olmuş, memnun</v>
+        <v>His, duyu, mantık</v>
       </c>
       <c r="C400" t="str">
-        <v>Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D400" t="str">
         <v>Feelings and Emotions</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Citizen</v>
+        <v>Community</v>
       </c>
       <c r="B413" t="str">
-        <v>Vatandaş, yurttaş</v>
+        <v>Topluluk, camia</v>
       </c>
       <c r="C413" t="str">
         <v>Noun</v>
@@ -6365,13 +6365,13 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Infant</v>
+        <v>Teenage</v>
       </c>
       <c r="B427" t="str">
-        <v>Bebek, süt çocuğu</v>
+        <v>Ergen, gençlik dönemindeki</v>
       </c>
       <c r="C427" t="str">
-        <v>Noun</v>
+        <v>Adjective</v>
       </c>
       <c r="D427" t="str">
         <v>People and Society</v>
@@ -6477,10 +6477,10 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Peer</v>
+        <v>Character</v>
       </c>
       <c r="B435" t="str">
-        <v>Akran, yaşıt</v>
+        <v>Karakter, kişilik</v>
       </c>
       <c r="C435" t="str">
         <v>Noun</v>
@@ -6547,10 +6547,10 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Bay</v>
+        <v>Land</v>
       </c>
       <c r="B440" t="str">
-        <v>Koy, körfez</v>
+        <v>Kara, toprak, arazi</v>
       </c>
       <c r="C440" t="str">
         <v>Noun</v>
@@ -6771,10 +6771,10 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Horizon</v>
+        <v>Ground</v>
       </c>
       <c r="B456" t="str">
-        <v>Ufuk çizgisi</v>
+        <v>Yer, zemin, toprak</v>
       </c>
       <c r="C456" t="str">
         <v>Noun</v>
@@ -6841,10 +6841,10 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Pond</v>
+        <v>Frog</v>
       </c>
       <c r="B461" t="str">
-        <v>Gölet, küçük havuz</v>
+        <v>Kurbağa</v>
       </c>
       <c r="C461" t="str">
         <v>Noun</v>
@@ -7247,10 +7247,10 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Outlet</v>
+        <v>Sale</v>
       </c>
       <c r="B490" t="str">
-        <v>Satış mağazası, outlet</v>
+        <v>İndirim, satış</v>
       </c>
       <c r="C490" t="str">
         <v>Noun</v>
@@ -7597,10 +7597,10 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Championship</v>
+        <v>Adventure</v>
       </c>
       <c r="B515" t="str">
-        <v>Şampiyona</v>
+        <v>Macera</v>
       </c>
       <c r="C515" t="str">
         <v>Noun</v>
@@ -7793,10 +7793,10 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Opponent</v>
+        <v>Audience</v>
       </c>
       <c r="B529" t="str">
-        <v>Rakip, karşı taraf</v>
+        <v>Seyirci, izleyici kitlesi</v>
       </c>
       <c r="C529" t="str">
         <v>Noun</v>
@@ -7821,13 +7821,13 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Referee</v>
+        <v>Beat</v>
       </c>
       <c r="B531" t="str">
-        <v>Hakem</v>
+        <v>Yenmek, mağlup etmek</v>
       </c>
       <c r="C531" t="str">
-        <v>Noun</v>
+        <v>Verb</v>
       </c>
       <c r="D531" t="str">
         <v>Sports and Hobbies</v>
@@ -7933,13 +7933,13 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Tournament</v>
+        <v>Cycle</v>
       </c>
       <c r="B539" t="str">
-        <v>Turnuva</v>
+        <v>Bisiklet sürmek, döngü</v>
       </c>
       <c r="C539" t="str">
-        <v>Noun</v>
+        <v>Noun / Verb</v>
       </c>
       <c r="D539" t="str">
         <v>Sports and Hobbies</v>
@@ -7947,10 +7947,10 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Trophy</v>
+        <v>Prize</v>
       </c>
       <c r="B540" t="str">
-        <v>Kupa, ödül</v>
+        <v>Ödül, mükâfat</v>
       </c>
       <c r="C540" t="str">
         <v>Noun</v>
@@ -7975,13 +7975,13 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Annual</v>
+        <v>Secondly</v>
       </c>
       <c r="B542" t="str">
-        <v>Yıllık, senede bir olan</v>
+        <v>İkinci olarak</v>
       </c>
       <c r="C542" t="str">
-        <v>Adjective</v>
+        <v>Adverb</v>
       </c>
       <c r="D542" t="str">
         <v>Time and Dates</v>
@@ -7989,10 +7989,10 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Constantly</v>
+        <v>Quietly</v>
       </c>
       <c r="B543" t="str">
-        <v>Sürekli olarak, durmaksızın</v>
+        <v>Sessizce, sakince</v>
       </c>
       <c r="C543" t="str">
         <v>Adverb</v>
@@ -8087,10 +8087,10 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Frequency</v>
+        <v>Speed</v>
       </c>
       <c r="B550" t="str">
-        <v>Sıklık</v>
+        <v>Hız, sürat</v>
       </c>
       <c r="C550" t="str">
         <v>Noun</v>
@@ -8129,13 +8129,13 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Instant</v>
+        <v>Step</v>
       </c>
       <c r="B553" t="str">
-        <v>An, anlık</v>
+        <v>Adım, aşama</v>
       </c>
       <c r="C553" t="str">
-        <v>Noun / Adjective</v>
+        <v>Noun</v>
       </c>
       <c r="D553" t="str">
         <v>Time and Dates</v>
@@ -8171,13 +8171,13 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Occasionally</v>
+        <v>After</v>
       </c>
       <c r="B556" t="str">
-        <v>Ara sıra, bazen</v>
+        <v>Sonra, ardından</v>
       </c>
       <c r="C556" t="str">
-        <v>Adverb</v>
+        <v>Adverb / Preposition</v>
       </c>
       <c r="D556" t="str">
         <v>Time and Dates</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Seldom</v>
+        <v>Yet</v>
       </c>
       <c r="B566" t="str">
-        <v>Nadiren, seyrek</v>
+        <v>Henüz, hala</v>
       </c>
       <c r="C566" t="str">
         <v>Adverb</v>
@@ -9221,10 +9221,10 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Forbid</v>
+        <v>Disagree</v>
       </c>
       <c r="B631" t="str">
-        <v>Yasaklamak</v>
+        <v>Aynı fikirde olmamak, katılmamak</v>
       </c>
       <c r="C631" t="str">
         <v>Verb</v>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Gain</v>
+        <v>Achieve</v>
       </c>
       <c r="B634" t="str">
-        <v>Kazanmak, elde etmek</v>
+        <v>Başarmak, elde etmek</v>
       </c>
       <c r="C634" t="str">
         <v>Verb</v>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Insist</v>
+        <v>Count</v>
       </c>
       <c r="B648" t="str">
-        <v>Israr etmek</v>
+        <v>Saymak, hesaba katmak</v>
       </c>
       <c r="C648" t="str">
         <v>Verb</v>
@@ -9627,10 +9627,10 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Maintain</v>
+        <v>Cover</v>
       </c>
       <c r="B660" t="str">
-        <v>Korumak, bakımını sağlamak</v>
+        <v>Örtmek, kapsamak</v>
       </c>
       <c r="C660" t="str">
         <v>Verb</v>
@@ -9781,10 +9781,10 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Obey</v>
+        <v>React</v>
       </c>
       <c r="B671" t="str">
-        <v>İtaat etmek, söz dinlemek</v>
+        <v>Tepki vermek, karşılık vermek</v>
       </c>
       <c r="C671" t="str">
         <v>Verb</v>
@@ -9809,10 +9809,10 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Operate</v>
+        <v>Act</v>
       </c>
       <c r="B673" t="str">
-        <v>Çalıştırmak, ameliyat etmek</v>
+        <v>Davranmak, hareket etmek</v>
       </c>
       <c r="C673" t="str">
         <v>Verb</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Permit</v>
+        <v>Depend</v>
       </c>
       <c r="B676" t="str">
-        <v>İzin vermek</v>
+        <v>Bağlı olmak, güvenmek</v>
       </c>
       <c r="C676" t="str">
         <v>Verb</v>
@@ -10103,10 +10103,10 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Regret</v>
+        <v>Realize</v>
       </c>
       <c r="B694" t="str">
-        <v>Pişman olmak</v>
+        <v>Fark etmek, idrak etmek</v>
       </c>
       <c r="C694" t="str">
         <v>Verb</v>
@@ -10411,10 +10411,10 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>Settle</v>
+        <v>Exist</v>
       </c>
       <c r="B716" t="str">
-        <v>Yerleşmek, halletmek</v>
+        <v>Var olmak, bulunmak</v>
       </c>
       <c r="C716" t="str">
         <v>Verb</v>
@@ -10677,10 +10677,10 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>Surround</v>
+        <v>Involve</v>
       </c>
       <c r="B735" t="str">
-        <v>Kuşatmak, çevrelemek</v>
+        <v>İçermek, kapsamak, gerektirmek</v>
       </c>
       <c r="C735" t="str">
         <v>Verb</v>
@@ -10901,10 +10901,10 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>Absolute</v>
+        <v>Certain</v>
       </c>
       <c r="B751" t="str">
-        <v>Kesin, mutlak</v>
+        <v>Belirli, kesin, emin</v>
       </c>
       <c r="C751" t="str">
         <v>Adjective</v>
@@ -10915,13 +10915,13 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>Accurate</v>
+        <v>Correctly</v>
       </c>
       <c r="B752" t="str">
-        <v>Doğru, hatasız, tam</v>
+        <v>Doğru bir şekilde</v>
       </c>
       <c r="C752" t="str">
-        <v>Adjective</v>
+        <v>Adverb</v>
       </c>
       <c r="D752" t="str">
         <v>Descriptive Adjectives</v>
@@ -10943,10 +10943,10 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>Actual</v>
+        <v>Everyday</v>
       </c>
       <c r="B754" t="str">
-        <v>Fiili, gerçek</v>
+        <v>Günlük, gündelik</v>
       </c>
       <c r="C754" t="str">
         <v>Adjective</v>
@@ -10971,10 +10971,10 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>Adequate</v>
+        <v>Creative</v>
       </c>
       <c r="B756" t="str">
-        <v>Yeterli, kafi</v>
+        <v>Yaratıcı</v>
       </c>
       <c r="C756" t="str">
         <v>Adjective</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>Appropriate</v>
+        <v>Tidy</v>
       </c>
       <c r="B762" t="str">
-        <v>Uygun, yerinde</v>
+        <v>Düzenli, tertipli</v>
       </c>
       <c r="C762" t="str">
         <v>Adjective</v>
@@ -11083,10 +11083,10 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>Automatic</v>
+        <v>Electrical</v>
       </c>
       <c r="B764" t="str">
-        <v>Otomatik</v>
+        <v>Elektrikli</v>
       </c>
       <c r="C764" t="str">
         <v>Adjective</v>
@@ -11097,10 +11097,10 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>Automatically</v>
+        <v>Differently</v>
       </c>
       <c r="B765" t="str">
-        <v>Otomatik olarak</v>
+        <v>Farklı bir şekilde</v>
       </c>
       <c r="C765" t="str">
         <v>Adverb</v>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>Basically</v>
+        <v>Nearly</v>
       </c>
       <c r="B770" t="str">
-        <v>Esasen, temel olarak</v>
+        <v>Neredeyse, hemen hemen</v>
       </c>
       <c r="C770" t="str">
         <v>Adverb</v>
@@ -11377,10 +11377,10 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>Curious</v>
+        <v>Informal</v>
       </c>
       <c r="B785" t="str">
-        <v>Meraklı, ilginç</v>
+        <v>Resmi olmayan, samimi</v>
       </c>
       <c r="C785" t="str">
         <v>Adjective</v>
@@ -11545,10 +11545,10 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>Efficient</v>
+        <v>Social</v>
       </c>
       <c r="B797" t="str">
-        <v>Verimli, randımanlı</v>
+        <v>Sosyal, toplumsal</v>
       </c>
       <c r="C797" t="str">
         <v>Adjective</v>
@@ -11573,10 +11573,10 @@
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>Elegant</v>
+        <v>Classical</v>
       </c>
       <c r="B799" t="str">
-        <v>Zarif, şık</v>
+        <v>Klasik</v>
       </c>
       <c r="C799" t="str">
         <v>Adjective</v>
@@ -11615,10 +11615,10 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>Entire</v>
+        <v>Closed</v>
       </c>
       <c r="B802" t="str">
-        <v>Bütün, tüm</v>
+        <v>Kapalı</v>
       </c>
       <c r="C802" t="str">
         <v>Adjective</v>
@@ -11713,10 +11713,10 @@
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>Extraordinary</v>
+        <v>Scary</v>
       </c>
       <c r="B809" t="str">
-        <v>Olağanüstü, fevkalade</v>
+        <v>Korkutucu, ürkütücü</v>
       </c>
       <c r="C809" t="str">
         <v>Adjective</v>
@@ -11909,13 +11909,13 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>Firm</v>
+        <v>Broken</v>
       </c>
       <c r="B823" t="str">
-        <v>Sıkı, sağlam, firma</v>
+        <v>Kırık, bozuk</v>
       </c>
       <c r="C823" t="str">
-        <v>Adjective / Noun</v>
+        <v>Adjective</v>
       </c>
       <c r="D823" t="str">
         <v>Descriptive Adjectives</v>
@@ -11951,13 +11951,13 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>Fortunate</v>
+        <v>Happily</v>
       </c>
       <c r="B826" t="str">
-        <v>Şanslı, talihli</v>
+        <v>Mutlu bir şekilde</v>
       </c>
       <c r="C826" t="str">
-        <v>Adjective</v>
+        <v>Adverb</v>
       </c>
       <c r="D826" t="str">
         <v>Descriptive Adjectives</v>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>Gorgeous</v>
+        <v>Fun</v>
       </c>
       <c r="B837" t="str">
-        <v>Göz alıcı, muhteşem</v>
+        <v>Eğlenceli, zevkli</v>
       </c>
       <c r="C837" t="str">
         <v>Adjective</v>
@@ -12119,10 +12119,10 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>Grand</v>
+        <v>Musical</v>
       </c>
       <c r="B838" t="str">
-        <v>Görkemli, büyük</v>
+        <v>Müzikal, müzikli</v>
       </c>
       <c r="C838" t="str">
         <v>Adjective</v>
@@ -12133,10 +12133,10 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>Handy</v>
+        <v>Able</v>
       </c>
       <c r="B839" t="str">
-        <v>Kullanışlı, elverişli</v>
+        <v>Yapabilen, muktedir</v>
       </c>
       <c r="C839" t="str">
         <v>Adjective</v>
@@ -12147,10 +12147,10 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>Harmful</v>
+        <v>Stupid</v>
       </c>
       <c r="B840" t="str">
-        <v>Zararlı</v>
+        <v>Aptalca, saçma</v>
       </c>
       <c r="C840" t="str">
         <v>Adjective</v>
@@ -12161,10 +12161,10 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>Harsh</v>
+        <v>Strange</v>
       </c>
       <c r="B841" t="str">
-        <v>Sert, haşin, kaba</v>
+        <v>Garip, tuhaf</v>
       </c>
       <c r="C841" t="str">
         <v>Adjective</v>
@@ -12315,10 +12315,10 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>Initial</v>
+        <v>Top</v>
       </c>
       <c r="B852" t="str">
-        <v>İlk, baştaki</v>
+        <v>En üst, tepe, zirve</v>
       </c>
       <c r="C852" t="str">
         <v>Adjective</v>
@@ -12329,10 +12329,10 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>Initially</v>
+        <v>Firstly</v>
       </c>
       <c r="B853" t="str">
-        <v>Başlangıçta, ilk olarak</v>
+        <v>İlk olarak, öncelikle</v>
       </c>
       <c r="C853" t="str">
         <v>Adverb</v>
@@ -12385,10 +12385,10 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>Internal</v>
+        <v>Inside</v>
       </c>
       <c r="B857" t="str">
-        <v>İç, dahili</v>
+        <v>İç, içerideki</v>
       </c>
       <c r="C857" t="str">
         <v>Adjective</v>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>Limited</v>
+        <v>Blank</v>
       </c>
       <c r="B864" t="str">
-        <v>Sınırlı, kısıtlı</v>
+        <v>Boş, temiz</v>
       </c>
       <c r="C864" t="str">
         <v>Adjective</v>
@@ -12511,10 +12511,10 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>Logical</v>
+        <v>Straight</v>
       </c>
       <c r="B866" t="str">
-        <v>Mantıklı</v>
+        <v>Düz, doğru</v>
       </c>
       <c r="C866" t="str">
         <v>Adjective</v>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>Loose</v>
+        <v>Lost</v>
       </c>
       <c r="B867" t="str">
-        <v>Gevşek, bol (kıyafet)</v>
+        <v>Kayıp, kaybolmuş</v>
       </c>
       <c r="C867" t="str">
         <v>Adjective</v>
@@ -12609,10 +12609,10 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>Massive</v>
+        <v>Middle</v>
       </c>
       <c r="B873" t="str">
-        <v>Çok büyük, heybetli</v>
+        <v>Orta, ortadaki</v>
       </c>
       <c r="C873" t="str">
         <v>Adjective</v>
@@ -12623,13 +12623,13 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>Maximum</v>
+        <v>Amount</v>
       </c>
       <c r="B874" t="str">
-        <v>Maksimum, en fazla</v>
+        <v>Miktar, tutar</v>
       </c>
       <c r="C874" t="str">
-        <v>Adjective / Noun</v>
+        <v>Noun</v>
       </c>
       <c r="D874" t="str">
         <v>Descriptive Adjectives</v>
@@ -12665,13 +12665,13 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>Military</v>
+        <v>Army</v>
       </c>
       <c r="B877" t="str">
-        <v>Askeri</v>
+        <v>Ordu, askeriye</v>
       </c>
       <c r="C877" t="str">
-        <v>Adjective / Noun</v>
+        <v>Noun</v>
       </c>
       <c r="D877" t="str">
         <v>Descriptive Adjectives</v>
@@ -12679,13 +12679,13 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>Minimum</v>
+        <v>Bit</v>
       </c>
       <c r="B878" t="str">
-        <v>Asgari, en az</v>
+        <v>Biraz, küçük parça</v>
       </c>
       <c r="C878" t="str">
-        <v>Adjective / Noun</v>
+        <v>Noun</v>
       </c>
       <c r="D878" t="str">
         <v>Descriptive Adjectives</v>
@@ -12693,10 +12693,10 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>Modest</v>
+        <v>Curly</v>
       </c>
       <c r="B879" t="str">
-        <v>Mütevazı, alçakgönüllü</v>
+        <v>Kıvırcık</v>
       </c>
       <c r="C879" t="str">
         <v>Adjective</v>
@@ -12749,10 +12749,10 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>Neat</v>
+        <v>Asleep</v>
       </c>
       <c r="B883" t="str">
-        <v>Düzenli, tertipli</v>
+        <v>Uykuda, uyuyan</v>
       </c>
       <c r="C883" t="str">
         <v>Adjective</v>
@@ -12791,10 +12791,10 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>Noble</v>
+        <v>Brilliant</v>
       </c>
       <c r="B886" t="str">
-        <v>Asil, soylu</v>
+        <v>Parlak, harika, zeki</v>
       </c>
       <c r="C886" t="str">
         <v>Adjective</v>
@@ -13015,10 +13015,10 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>Permanent</v>
+        <v>Traditional</v>
       </c>
       <c r="B902" t="str">
-        <v>Kalıcı, sürekli</v>
+        <v>Geleneksel</v>
       </c>
       <c r="C902" t="str">
         <v>Adjective</v>
@@ -13071,13 +13071,13 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>Plain</v>
+        <v>Connected</v>
       </c>
       <c r="B906" t="str">
-        <v>Sade, düz, ova</v>
+        <v>Bağlantılı, bağlı</v>
       </c>
       <c r="C906" t="str">
-        <v>Adjective / Noun</v>
+        <v>Adjective</v>
       </c>
       <c r="D906" t="str">
         <v>Descriptive Adjectives</v>
@@ -13183,10 +13183,10 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>Precious</v>
+        <v>International</v>
       </c>
       <c r="B914" t="str">
-        <v>Değerli, kıymetli</v>
+        <v>Uluslararası</v>
       </c>
       <c r="C914" t="str">
         <v>Adjective</v>
@@ -13281,10 +13281,10 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>Pure</v>
+        <v>Divorced</v>
       </c>
       <c r="B921" t="str">
-        <v>Saf, arı, katıksız</v>
+        <v>Boşanmış</v>
       </c>
       <c r="C921" t="str">
         <v>Adjective</v>
@@ -13365,10 +13365,10 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>Reasonable</v>
+        <v>All right</v>
       </c>
       <c r="B927" t="str">
-        <v>Makul, akla yatkın</v>
+        <v>Uygun, yolunda, iyi</v>
       </c>
       <c r="C927" t="str">
         <v>Adjective</v>
@@ -13393,10 +13393,10 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>Relevant</v>
+        <v>Included</v>
       </c>
       <c r="B929" t="str">
-        <v>İlgili, alakalı</v>
+        <v>Dahil, kapsanmış</v>
       </c>
       <c r="C929" t="str">
         <v>Adjective</v>
@@ -13407,10 +13407,10 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>Remarkable</v>
+        <v>Secret</v>
       </c>
       <c r="B930" t="str">
-        <v>Dikkate değer, olağanüstü</v>
+        <v>Gizli, sır</v>
       </c>
       <c r="C930" t="str">
         <v>Adjective</v>
@@ -13435,10 +13435,10 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>Secure</v>
+        <v>United</v>
       </c>
       <c r="B932" t="str">
-        <v>Güvenli, emniyette</v>
+        <v>Birleşik, birleşmiş</v>
       </c>
       <c r="C932" t="str">
         <v>Adjective</v>
@@ -13477,10 +13477,10 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>Severe</v>
+        <v>Worse</v>
       </c>
       <c r="B935" t="str">
-        <v>Şiddetli, ağır, sert</v>
+        <v>Daha kötü</v>
       </c>
       <c r="C935" t="str">
         <v>Adjective</v>
@@ -13547,10 +13547,10 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>Sincere</v>
+        <v>Professional</v>
       </c>
       <c r="B940" t="str">
-        <v>Samimi, içten</v>
+        <v>Profesyonel, mesleki</v>
       </c>
       <c r="C940" t="str">
         <v>Adjective</v>
@@ -13561,10 +13561,10 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>Slight</v>
+        <v>Missing</v>
       </c>
       <c r="B941" t="str">
-        <v>Hafif, az</v>
+        <v>Eksik, kayıp</v>
       </c>
       <c r="C941" t="str">
         <v>Adjective</v>
@@ -13659,13 +13659,13 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>Strict</v>
+        <v>Badly</v>
       </c>
       <c r="B948" t="str">
-        <v>Katı, disiplinli</v>
+        <v>Kötü bir şekilde, ağır</v>
       </c>
       <c r="C948" t="str">
-        <v>Adjective</v>
+        <v>Adverb</v>
       </c>
       <c r="D948" t="str">
         <v>Descriptive Adjectives</v>
@@ -13729,10 +13729,10 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>Temporary</v>
+        <v>Bottom</v>
       </c>
       <c r="B953" t="str">
-        <v>Geçici</v>
+        <v>Alt, dip</v>
       </c>
       <c r="C953" t="str">
         <v>Adjective</v>
@@ -13743,10 +13743,10 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>Tough</v>
+        <v>Worst</v>
       </c>
       <c r="B954" t="str">
-        <v>Zorlu, sert, dayanıklı</v>
+        <v>En kötü</v>
       </c>
       <c r="C954" t="str">
         <v>Adjective</v>
@@ -13757,10 +13757,10 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>Truly</v>
+        <v>Loudly</v>
       </c>
       <c r="B955" t="str">
-        <v>Hakikaten, gerçekten</v>
+        <v>Yüksek sesle</v>
       </c>
       <c r="C955" t="str">
         <v>Adverb</v>
@@ -13813,10 +13813,10 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>Urgent</v>
+        <v>Further</v>
       </c>
       <c r="B959" t="str">
-        <v>Acil, ivedi</v>
+        <v>Daha fazla, ilave</v>
       </c>
       <c r="C959" t="str">
         <v>Adjective</v>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>Useless</v>
+        <v>Plastic</v>
       </c>
       <c r="B961" t="str">
-        <v>Faydasız, işe yaramaz</v>
+        <v>Plastik</v>
       </c>
       <c r="C961" t="str">
         <v>Adjective</v>
@@ -13883,10 +13883,10 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>Vast</v>
+        <v>National</v>
       </c>
       <c r="B964" t="str">
-        <v>Uçsuz bucaksız, engin</v>
+        <v>Ulusal, milli</v>
       </c>
       <c r="C964" t="str">
         <v>Adjective</v>
@@ -13911,10 +13911,10 @@
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>Visible</v>
+        <v>Mobile</v>
       </c>
       <c r="B966" t="str">
-        <v>Görünür, belirgin</v>
+        <v>Taşınabilir, seyyar</v>
       </c>
       <c r="C966" t="str">
         <v>Adjective</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>Vital</v>
+        <v>Working</v>
       </c>
       <c r="B967" t="str">
-        <v>Hayati, çok önemli</v>
+        <v>Çalışan, işleyen</v>
       </c>
       <c r="C967" t="str">
         <v>Adjective</v>
@@ -13939,10 +13939,10 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>Wealthy</v>
+        <v>Following</v>
       </c>
       <c r="B968" t="str">
-        <v>Varlıklı, zengin</v>
+        <v>Aşağıdaki, sonraki</v>
       </c>
       <c r="C968" t="str">
         <v>Adjective</v>
@@ -13967,10 +13967,10 @@
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>Wise</v>
+        <v>Based</v>
       </c>
       <c r="B970" t="str">
-        <v>Bilge, akıllıca</v>
+        <v>Dayalı, esaslı</v>
       </c>
       <c r="C970" t="str">
         <v>Adjective</v>
@@ -14583,10 +14583,10 @@
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>Thread</v>
+        <v>Tool</v>
       </c>
       <c r="B1014" t="str">
-        <v>İplik, dikiş ipliği</v>
+        <v>Alet, el aleti</v>
       </c>
       <c r="C1014" t="str">
         <v>Noun</v>
